--- a/data/database/indicator_metrics.xlsx
+++ b/data/database/indicator_metrics.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,6 +456,22 @@
         <v>5</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/database/indicator_metrics.xlsx
+++ b/data/database/indicator_metrics.xlsx
@@ -442,34 +442,34 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/data/database/indicator_metrics.xlsx
+++ b/data/database/indicator_metrics.xlsx
@@ -442,34 +442,34 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data/database/indicator_metrics.xlsx
+++ b/data/database/indicator_metrics.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,6 +472,14 @@
         <v>7</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/database/indicator_metrics.xlsx
+++ b/data/database/indicator_metrics.xlsx
@@ -442,42 +442,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/data/database/indicator_metrics.xlsx
+++ b/data/database/indicator_metrics.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,6 +480,14 @@
         <v>5</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" t="n">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
